--- a/resources/templates/standard/A6200-02.xlsx
+++ b/resources/templates/standard/A6200-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>분임조 활동 계획서</t>
   </si>
@@ -781,7 +784,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -789,7 +794,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -816,17 +821,17 @@
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
       <c r="AG1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH1" s="3"/>
       <c r="AI1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN1" s="4"/>
       <c r="AO1" s="4"/>
@@ -966,7 +971,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -989,7 +994,7 @@
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
       <c r="V5" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
@@ -998,7 +1003,7 @@
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
       <c r="AC5" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD5" s="9"/>
       <c r="AE5" s="9"/>
@@ -1016,7 +1021,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -1039,7 +1044,7 @@
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
       <c r="V6" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
@@ -1064,7 +1069,7 @@
     </row>
     <row r="7" ht="17.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1087,7 +1092,7 @@
       <c r="T7" s="15"/>
       <c r="U7" s="16"/>
       <c r="V7" s="17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W7" s="17"/>
       <c r="X7" s="17"/>
@@ -1096,7 +1101,7 @@
       <c r="AA7" s="17"/>
       <c r="AB7" s="17"/>
       <c r="AC7" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD7" s="15"/>
       <c r="AE7" s="15"/>
@@ -1142,7 +1147,7 @@
       <c r="AA8" s="17"/>
       <c r="AB8" s="17"/>
       <c r="AC8" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD8" s="20"/>
       <c r="AE8" s="20"/>
@@ -1160,7 +1165,7 @@
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -1426,7 +1431,7 @@
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
@@ -1692,7 +1697,7 @@
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -1720,7 +1725,7 @@
       <c r="Y21" s="10"/>
       <c r="Z21" s="10"/>
       <c r="AA21" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AB21" s="12"/>
       <c r="AC21" s="12"/>
@@ -1732,7 +1737,7 @@
       <c r="AI21" s="12"/>
       <c r="AJ21" s="12"/>
       <c r="AK21" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL21" s="12"/>
       <c r="AM21" s="12"/>
@@ -2226,7 +2231,7 @@
     </row>
     <row r="33" ht="20.1" customHeight="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -2306,13 +2311,13 @@
       <c r="AG34" s="6"/>
       <c r="AH34" s="6"/>
       <c r="AI34" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ34" s="11"/>
       <c r="AK34" s="11"/>
       <c r="AL34" s="11"/>
       <c r="AM34" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN34" s="11"/>
       <c r="AO34" s="11"/>
